--- a/expenses.xlsx
+++ b/expenses.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,6 +576,29 @@
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>500</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>12-03-2025</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>strawberry and cigarettes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
